--- a/src/nodes/HPC/compressor_stage_6_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_6_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>4.8390306131284309</v>
+        <v>4.2544849904987929</v>
       </c>
       <c r="B1">
-        <v>8.3490024854833518</v>
+        <v>8.6614904746828536</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.2362833737685364</v>
+        <v>3.665345628452767</v>
       </c>
       <c r="B2">
-        <v>8.171484256027659</v>
+        <v>8.4430144612784961</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.6992185146082708</v>
+        <v>3.145566155439397</v>
       </c>
       <c r="B3">
-        <v>7.9381373111392337</v>
+        <v>8.1733503015027864</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.1799808624963855</v>
+        <v>2.6446120218683515</v>
       </c>
       <c r="B4">
-        <v>7.689637595199585</v>
+        <v>7.8897928924110232</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.675676921658289</v>
+        <v>2.1594277272350482</v>
       </c>
       <c r="B5">
-        <v>7.4284445220075792</v>
+        <v>7.5945972175282384</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.1850020158347743</v>
+        <v>1.6886355474027073</v>
       </c>
       <c r="B6">
-        <v>7.1556670404074252</v>
+        <v>7.2887800481577942</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.7071403897530282</v>
+        <v>1.2313740535523967</v>
       </c>
       <c r="B7">
-        <v>6.8719985261393148</v>
+        <v>6.9729771255773514</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.2415419513777011</v>
+        <v>0.78706235439464589</v>
       </c>
       <c r="B8">
-        <v>6.5779065464809587</v>
+        <v>6.6476171521502785</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.78747784960744727</v>
+        <v>0.35493079098352287</v>
       </c>
       <c r="B9">
-        <v>6.2740106103570676</v>
+        <v>6.313268142262551</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.34418557129268967</v>
+        <v>-0.06582584238880046</v>
       </c>
       <c r="B10">
-        <v>5.9609588387631334</v>
+        <v>5.9705243440914142</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.089053285843082239</v>
+        <v>-0.47596617082129589</v>
       </c>
       <c r="B11">
-        <v>5.639361859330795</v>
+        <v>5.6199456289565681</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.51267375231956991</v>
+        <v>-0.875949581876968</v>
       </c>
       <c r="B12">
-        <v>5.309589439340332</v>
+        <v>5.2618710285108072</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.9260214825022911</v>
+        <v>-1.2650850935838072</v>
       </c>
       <c r="B13">
-        <v>4.9710853980304677</v>
+        <v>4.8957905925968195</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.3287379034844618</v>
+        <v>-1.6429940567980239</v>
       </c>
       <c r="B14">
-        <v>4.6235449555696251</v>
+        <v>4.5214248751534063</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.7227369094242619</v>
+        <v>-2.011697523223714</v>
       </c>
       <c r="B15">
-        <v>4.2685948838866015</v>
+        <v>4.1402654283138789</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.1097731518540841</v>
+        <v>-2.3730483860600571</v>
       </c>
       <c r="B16">
-        <v>3.9077266018488022</v>
+        <v>3.7536797019056998</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.4886918447382116</v>
+        <v>-2.7258272036386728</v>
       </c>
       <c r="B17">
-        <v>3.5399585643176645</v>
+        <v>3.3607677383383452</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.8579759870054109</v>
+        <v>-3.0684320390985134</v>
       </c>
       <c r="B18">
-        <v>3.1640013505861533</v>
+        <v>2.9603472955456254</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.217569155010533</v>
+        <v>-3.4008033096754571</v>
       </c>
       <c r="B19">
-        <v>2.7798070016792864</v>
+        <v>2.5523744009766363</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.5677800694649444</v>
+        <v>-3.7232670211296073</v>
       </c>
       <c r="B20">
-        <v>2.3876379240550913</v>
+        <v>2.1370896494592935</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.9089174510800104</v>
+        <v>-4.0361491792210717</v>
       </c>
       <c r="B21">
-        <v>1.9877565241716009</v>
+        <v>1.7147336358215191</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.24123189300609</v>
+        <v>-4.339714407628958</v>
       </c>
       <c r="B22">
-        <v>1.580375801217301</v>
+        <v>1.2855016544302464</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.5647414781494984</v>
+        <v>-4.6339818017083916</v>
       </c>
       <c r="B23">
-        <v>1.16551112530253</v>
+        <v>0.84940779780850173</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.8794061618555356</v>
+        <v>-4.9189090747334987</v>
       </c>
       <c r="B24">
-        <v>0.74312845926808369</v>
+        <v>0.4064208580183285</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.1851858994695048</v>
+        <v>-5.1944539399784091</v>
       </c>
       <c r="B25">
-        <v>0.31319376595476123</v>
+        <v>-0.043490372878226755</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.4820251686549506</v>
+        <v>-5.4605577664513119</v>
       </c>
       <c r="B26">
-        <v>-0.12434014751797495</v>
+        <v>-0.50036916501657513</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.7698065363483684</v>
+        <v>-5.717096546096645</v>
       </c>
       <c r="B27">
-        <v>-0.56957309691601288</v>
+        <v>-0.964307037321966</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.0483970918044969</v>
+        <v>-5.9639299265929075</v>
       </c>
       <c r="B28">
-        <v>-1.0226180537265686</v>
+        <v>-1.4354075709171001</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.3176639242780723</v>
+        <v>-6.2009175556185987</v>
       </c>
       <c r="B29">
-        <v>-1.4835879894368611</v>
+        <v>-1.9137743469246795</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.5775041067203714</v>
+        <v>-6.4279507433141827</v>
       </c>
       <c r="B30">
-        <v>-1.9525703899890279</v>
+        <v>-2.399487579320196</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-6.8279346468688269</v>
+        <v>-6.6450474496679774</v>
       </c>
       <c r="B31">
-        <v>-2.42955079914487</v>
+        <v>-2.8925340134903008</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.0690025361574182</v>
+        <v>-6.85225729713027</v>
       </c>
       <c r="B32">
-        <v>-2.9144892751211158</v>
+        <v>-3.392877027674444</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.3007547660201135</v>
+        <v>-7.0496299081513385</v>
       </c>
       <c r="B33">
-        <v>-3.4073458761344808</v>
+        <v>-3.9004800001120623</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.5231659830271367</v>
+        <v>-7.2371385097812615</v>
       </c>
       <c r="B34">
-        <v>-3.9081421520954973</v>
+        <v>-4.4153626894518379</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-7.7359214542936865</v>
+        <v>-7.4144507474692656</v>
       </c>
       <c r="B35">
-        <v>-4.4171456196899026</v>
+        <v>-4.9377703759793734</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-7.9386341020712106</v>
+        <v>-7.5811578712643781</v>
       </c>
       <c r="B36">
-        <v>-4.9346852872972464</v>
+        <v>-5.4680047203895183</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.13091684861116</v>
+        <v>-7.7368511312156247</v>
       </c>
       <c r="B37">
-        <v>-5.4610901632970794</v>
+        <v>-6.0063673833771185</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.31221884376157</v>
+        <v>-7.8809488354705213</v>
       </c>
       <c r="B38">
-        <v>-5.9968284593511276</v>
+        <v>-6.5532876581273634</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.4813341477568684</v>
+        <v>-8.0121775245705962</v>
       </c>
       <c r="B39">
-        <v>-6.5429252002498632</v>
+        <v>-7.10970536778686</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-8.636893048428071</v>
+        <v>-8.1290907971558664</v>
       </c>
       <c r="B40">
-        <v>-7.1005446140659325</v>
+        <v>-7.676687967992553</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-8.77752583360619</v>
+        <v>-8.2302422518663558</v>
       </c>
       <c r="B41">
-        <v>-7.6708509288719853</v>
+        <v>-8.2553029143814012</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-8.77752583360619</v>
+        <v>-8.2302422518663558</v>
       </c>
       <c r="B42">
-        <v>-7.6708509288719853</v>
+        <v>-8.2553029143814012</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-8.584161167775477</v>
+        <v>-8.0734064967478911</v>
       </c>
       <c r="B43">
-        <v>-7.14536566272828</v>
+        <v>-7.7177834218582309</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.38492666990928</v>
+        <v>-7.9103722619552084</v>
       </c>
       <c r="B44">
-        <v>-6.624869636946312</v>
+        <v>-7.1848384563314127</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.1789602262734977</v>
+        <v>-7.7402291646314607</v>
       </c>
       <c r="B45">
-        <v>-6.1100956310353691</v>
+        <v>-6.6571398875455445</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-7.96539972313404</v>
+        <v>-7.5620668219198128</v>
       </c>
       <c r="B46">
-        <v>-5.6017764245047417</v>
+        <v>-6.1353595852452347</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-7.7435211785033253</v>
+        <v>-7.3751207166062418</v>
       </c>
       <c r="B47">
-        <v>-5.1005273876293753</v>
+        <v>-5.6200617691776591</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.5131531373798488</v>
+        <v>-7.179209794048055</v>
       </c>
       <c r="B48">
-        <v>-4.6064942537468889</v>
+        <v>-5.1113800591003065</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.2742622765086162</v>
+        <v>-6.9742988652453795</v>
       </c>
       <c r="B49">
-        <v>-4.1197053469605533</v>
+        <v>-4.6093404247732366</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.0268152726346358</v>
+        <v>-6.76035274119834</v>
       </c>
       <c r="B50">
-        <v>-3.6401889913736429</v>
+        <v>-4.1139688359565065</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-6.7708295201508539</v>
+        <v>-6.53738979019933</v>
       </c>
       <c r="B51">
-        <v>-3.1679304020984853</v>
+        <v>-3.6252517367051467</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.5065252840419268</v>
+        <v>-6.3056426097097562</v>
       </c>
       <c r="B52">
-        <v>-2.70274235828359</v>
+        <v>-3.1430174682540279</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.2341735469404576</v>
+        <v>-6.0653973544832969</v>
       </c>
       <c r="B53">
-        <v>-2.2443945300865238</v>
+        <v>-2.6670548461329964</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.9540452914790354</v>
+        <v>-5.816940179273618</v>
       </c>
       <c r="B54">
-        <v>-1.7926565876648435</v>
+        <v>-2.1971526858718837</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.6663652194712606</v>
+        <v>-5.5605083667859079</v>
       </c>
       <c r="B55">
-        <v>-1.3473375389508069</v>
+        <v>-1.7331358709586302</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.3711729094547609</v>
+        <v>-5.296143711531407</v>
       </c>
       <c r="B56">
-        <v>-0.90840374297544058</v>
+        <v>-1.2749735567135681</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.0684616591481664</v>
+        <v>-5.0238391359728745</v>
       </c>
       <c r="B57">
-        <v>-0.47586089654446739</v>
+        <v>-0.82267096641512827</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.7582247662701063</v>
+        <v>-4.7435875625730688</v>
       </c>
       <c r="B58">
-        <v>-0.049714696463609626</v>
+        <v>-0.37623332334174242</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.4404568416695644</v>
+        <v>-4.4553833004463144</v>
       </c>
       <c r="B59">
-        <v>0.37003027659606935</v>
+        <v>0.064335172587981229</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.1151577487169337</v>
+        <v>-4.1592262053132094</v>
       </c>
       <c r="B60">
-        <v>0.78337390650212091</v>
+        <v>0.49903441489470191</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.7823286639129572</v>
+        <v>-3.8551175195459244</v>
       </c>
       <c r="B61">
-        <v>1.1903171932567553</v>
+        <v>0.92786532045890135</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.441970763758381</v>
+        <v>-3.5430584855166258</v>
       </c>
       <c r="B62">
-        <v>1.59086113686218</v>
+        <v>1.3508288061610594</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.09412931385799</v>
+        <v>-3.2230969032184853</v>
       </c>
       <c r="B63">
-        <v>1.9850442121812222</v>
+        <v>1.7679601487739756</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.73902593623273</v>
+        <v>-2.8954668031286741</v>
       </c>
       <c r="B64">
-        <v>2.3730547935191932</v>
+        <v>2.1794320646397352</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.3769263420075877</v>
+        <v>-2.5604487733453691</v>
       </c>
       <c r="B65">
-        <v>2.7551187300420183</v>
+        <v>2.5854516299927397</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.0080962423075506</v>
+        <v>-2.218323401966745</v>
       </c>
       <c r="B66">
-        <v>3.1314618709156257</v>
+        <v>2.98622592106739</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.632424543222853</v>
+        <v>-1.8689733750155948</v>
       </c>
       <c r="B67">
-        <v>3.5019897885285936</v>
+        <v>3.3816683592211847</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.2482929307047141</v>
+        <v>-1.5106897702131867</v>
       </c>
       <c r="B68">
-        <v>3.8653269481601091</v>
+        <v>3.7705177463039923</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.85442792152374147</v>
+        <v>-1.1421278029276734</v>
       </c>
       <c r="B69">
-        <v>4.22039091442026</v>
+        <v>4.15178162062747</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.45244257586711911</v>
+        <v>-0.7649908474162902</v>
       </c>
       <c r="B70">
-        <v>4.5685527563520987</v>
+        <v>4.5267170858580217</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.044094749484076962</v>
+        <v>-0.38113518049683048</v>
       </c>
       <c r="B71">
-        <v>4.9113066163435484</v>
+        <v>4.89669408896039</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.37116506304451807</v>
+        <v>0.010019469659742521</v>
       </c>
       <c r="B72">
-        <v>5.2481854257290017</v>
+        <v>5.2612843847379027</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.79419993473440254</v>
+        <v>0.40938449890139683</v>
       </c>
       <c r="B73">
-        <v>5.5784555896288763</v>
+        <v>5.6198153558504966</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.2248198478193479</v>
+        <v>0.81675925050497677</v>
       </c>
       <c r="B74">
-        <v>5.9022786193612129</v>
+        <v>5.9724350885459829</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.6625707986686078</v>
+        <v>1.2316643015057058</v>
       </c>
       <c r="B75">
-        <v>6.2200404089729258</v>
+        <v>6.3194974007620353</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.1069959309753377</v>
+        <v>1.6536172165434409</v>
       </c>
       <c r="B76">
-        <v>6.5321292772288189</v>
+        <v>6.6613583336079172</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.5576949701779408</v>
+        <v>2.0821953099741695</v>
       </c>
       <c r="B77">
-        <v>6.83888544953678</v>
+        <v>6.998329832430092</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.0144968213719037</v>
+        <v>2.5172179074137566</v>
       </c>
       <c r="B78">
-        <v>7.140454353159142</v>
+        <v>7.3305452363522159</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.4769889447985332</v>
+        <v>2.9582493713016027</v>
       </c>
       <c r="B79">
-        <v>7.437186638677125</v>
+        <v>7.6583260493375738</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.944322271847907</v>
+        <v>3.4043930942920797</v>
       </c>
       <c r="B80">
-        <v>7.7298039975041952</v>
+        <v>7.9823339746945985</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.41410374666788</v>
+        <v>3.85312203507138</v>
       </c>
       <c r="B81">
-        <v>8.0203404794689046</v>
+        <v>8.3044339888882437</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>4.8390306131284309</v>
+        <v>4.2544849904987929</v>
       </c>
       <c r="B82">
-        <v>8.3490024854833518</v>
+        <v>8.6614904746828536</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.0014818178659715</v>
+        <v>4.3548569528491843</v>
       </c>
       <c r="B1">
-        <v>9.42170247251343</v>
+        <v>9.7374801039709862</v>
       </c>
       <c r="C1">
         <v>218.7117598010542</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.2752432088639827</v>
+        <v>3.60607297539098</v>
       </c>
       <c r="B2">
-        <v>9.2542726116574343</v>
+        <v>9.5457384853508689</v>
       </c>
       <c r="C2">
         <v>218.7117598010542</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.6658440788986382</v>
+        <v>3.0021295023140295</v>
       </c>
       <c r="B3">
-        <v>8.9947735480125619</v>
+        <v>9.2549264185665034</v>
       </c>
       <c r="C3">
         <v>218.7117598010542</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.0826128874400895</v>
+        <v>2.4287538275455542</v>
       </c>
       <c r="B4">
-        <v>8.7146542175125656</v>
+        <v>8.94320607415115</v>
       </c>
       <c r="C4">
         <v>218.7117598010542</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.5202438950619075</v>
+        <v>1.8793153849858673</v>
       </c>
       <c r="B5">
-        <v>8.4180955288984336</v>
+        <v>8.615112738403937</v>
       </c>
       <c r="C5">
         <v>218.7117598010542</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.9764317112502399</v>
+        <v>1.3509617345487632</v>
       </c>
       <c r="B6">
-        <v>8.10691412384367</v>
+        <v>8.272597471347126</v>
       </c>
       <c r="C6">
         <v>218.7117598010542</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.4497796485150729</v>
+        <v>0.841980037389947</v>
       </c>
       <c r="B7">
-        <v>7.7822105884242276</v>
+        <v>7.91683184934785</v>
       </c>
       <c r="C7">
         <v>218.7117598010542</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.9393863816856739</v>
+        <v>0.35127920896766207</v>
       </c>
       <c r="B8">
-        <v>7.4446951645087616</v>
+        <v>7.54856217079135</v>
       </c>
       <c r="C8">
         <v>218.7117598010542</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.44399205478726744</v>
+        <v>-0.12269000892279475</v>
       </c>
       <c r="B9">
-        <v>7.0953606152983975</v>
+        <v>7.1688481234032242</v>
       </c>
       <c r="C9">
         <v>218.7117598010542</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.037735777931279836</v>
+        <v>-0.58157116521098928</v>
       </c>
       <c r="B10">
-        <v>6.7352569045474917</v>
+        <v>6.7788138894674788</v>
       </c>
       <c r="C10">
         <v>218.7117598010542</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.50706139052249632</v>
+        <v>-1.02692679806299</v>
       </c>
       <c r="B11">
-        <v>6.3653802768908418</v>
+        <v>6.3795282401613962</v>
       </c>
       <c r="C11">
         <v>218.7117598010542</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.96471824378947546</v>
+        <v>-1.4596524052087621</v>
       </c>
       <c r="B12">
-        <v>5.9863086975160229</v>
+        <v>5.9716036931078413</v>
       </c>
       <c r="C12">
         <v>218.7117598010542</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.4093847172361673</v>
+        <v>-1.8780563333973417</v>
       </c>
       <c r="B13">
-        <v>5.5970007329412716</v>
+        <v>5.5538831628186918</v>
       </c>
       <c r="C13">
         <v>218.7117598010542</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.8403076140800512</v>
+        <v>-2.281165862475377</v>
       </c>
       <c r="B14">
-        <v>5.1968628660790293</v>
+        <v>5.1257013117770551</v>
       </c>
       <c r="C14">
         <v>218.7117598010542</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.2610625136918734</v>
+        <v>-2.6734711556608932</v>
       </c>
       <c r="B15">
-        <v>4.7887126440879024</v>
+        <v>4.69012939746191</v>
       </c>
       <c r="C15">
         <v>218.7117598010542</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.6749280474360191</v>
+        <v>-3.0590896519096558</v>
       </c>
       <c r="B16">
-        <v>4.3751336198769462</v>
+        <v>4.2499837351324423</v>
       </c>
       <c r="C16">
         <v>218.7117598010542</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.0796662784981925</v>
+        <v>-3.435185009757042</v>
       </c>
       <c r="B17">
-        <v>3.9543623051108545</v>
+        <v>3.8033242761727766</v>
       </c>
       <c r="C17">
         <v>218.7117598010542</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.4723579755761631</v>
+        <v>-3.7980638453708346</v>
       </c>
       <c r="B18">
-        <v>3.5240983531861643</v>
+        <v>3.3476247576907521</v>
       </c>
       <c r="C18">
         <v>218.7117598010542</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.852875297594665</v>
+        <v>-4.1475583858688578</v>
       </c>
       <c r="B19">
-        <v>3.0842410256711363</v>
+        <v>2.8827704235641249</v>
       </c>
       <c r="C19">
         <v>218.7117598010542</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.2217882510351776</v>
+        <v>-4.4843822611064486</v>
       </c>
       <c r="B20">
-        <v>2.6352394861769639</v>
+        <v>2.409249394363127</v>
       </c>
       <c r="C20">
         <v>218.7117598010542</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.5796668423791766</v>
+        <v>-4.809249100938942</v>
       </c>
       <c r="B21">
-        <v>2.1775428983148415</v>
+        <v>1.9275497906579928</v>
       </c>
       <c r="C21">
         <v>218.7117598010542</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.9269760023402354</v>
+        <v>-5.1227417171021363</v>
       </c>
       <c r="B22">
-        <v>1.7115176262666658</v>
+        <v>1.4380702538377956</v>
       </c>
       <c r="C22">
         <v>218.7117598010542</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.2637603585603125</v>
+        <v>-5.4249196488536784</v>
       </c>
       <c r="B23">
-        <v>1.2371988364971573</v>
+        <v>0.94085150856697863</v>
       </c>
       <c r="C23">
         <v>218.7117598010542</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.5899594629134581</v>
+        <v>-5.7157116173316806</v>
       </c>
       <c r="B24">
-        <v>0.75453889604174029</v>
+        <v>0.43584480032882655</v>
       </c>
       <c r="C24">
         <v>218.7117598010542</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.9055128672737291</v>
+        <v>-5.9950463436742538</v>
       </c>
       <c r="B25">
-        <v>0.26349017193583962</v>
+        <v>-0.076998625393377276</v>
       </c>
       <c r="C25">
         <v>218.7117598010542</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.2103360899796938</v>
+        <v>-6.2628239424310967</v>
       </c>
       <c r="B26">
-        <v>-0.23601390714799059</v>
+        <v>-0.59774708993259007</v>
       </c>
       <c r="C26">
         <v>218.7117598010542</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.5042485152280021</v>
+        <v>-6.5188301017982822</v>
       </c>
       <c r="B27">
-        <v>-0.74411566598870216</v>
+        <v>-1.1265471818867598</v>
       </c>
       <c r="C27">
         <v>218.7117598010542</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.787045493679817</v>
+        <v>-6.76282190338347</v>
       </c>
       <c r="B28">
-        <v>-1.26097636772811</v>
+        <v>-1.6635650566700693</v>
       </c>
       <c r="C28">
         <v>218.7117598010542</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.0585223759963007</v>
+        <v>-6.9945564287943185</v>
       </c>
       <c r="B29">
-        <v>-1.786757275508033</v>
+        <v>-2.2089668696967073</v>
       </c>
       <c r="C29">
         <v>218.7117598010542</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.3185376186616278</v>
+        <v>-7.213872294343723</v>
       </c>
       <c r="B30">
-        <v>-2.3215699252474042</v>
+        <v>-2.7628630068996403</v>
       </c>
       <c r="C30">
         <v>218.7117598010542</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.5672021014520165</v>
+        <v>-7.4209342551655126</v>
       </c>
       <c r="B31">
-        <v>-2.8653269439736087</v>
+        <v>-3.3251407762869709</v>
       </c>
       <c r="C31">
         <v>218.7117598010542</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.8046898099666979</v>
+        <v>-7.6159886010987554</v>
       </c>
       <c r="B32">
-        <v>-3.4178912314911556</v>
+        <v>-3.8956317163855925</v>
       </c>
       <c r="C32">
         <v>218.7117598010542</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.0311747298048974</v>
+        <v>-7.7992816219825141</v>
       </c>
       <c r="B33">
-        <v>-3.9791256876045438</v>
+        <v>-4.4741673657223888</v>
       </c>
       <c r="C33">
         <v>218.7117598010542</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.2467016344452375</v>
+        <v>-7.9708992656604707</v>
       </c>
       <c r="B34">
-        <v>-4.548995030930147</v>
+        <v>-5.0606889362433654</v>
       </c>
       <c r="C34">
         <v>218.7117598010542</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.4507984488839067</v>
+        <v>-8.1302861119947778</v>
       </c>
       <c r="B35">
-        <v>-5.1278712553318186</v>
+        <v>-5.6555763335709939</v>
       </c>
       <c r="C35">
         <v>218.7117598010542</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.6428638859964746</v>
+        <v>-8.2767263988522</v>
       </c>
       <c r="B36">
-        <v>-5.7162281734852858</v>
+        <v>-6.2593191367468606</v>
       </c>
       <c r="C36">
         <v>218.7117598010542</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.8222966586585265</v>
+        <v>-8.4095043640995044</v>
       </c>
       <c r="B37">
-        <v>-6.3145395980662764</v>
+        <v>-6.8724069248125605</v>
       </c>
       <c r="C37">
         <v>218.7117598010542</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.9881941509567316</v>
+        <v>-8.5275273436570611</v>
       </c>
       <c r="B38">
-        <v>-6.9235167880452186</v>
+        <v>-7.4955870765522574</v>
       </c>
       <c r="C38">
         <v>218.7117598010542</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.1384484318221233</v>
+        <v>-8.6281950656596553</v>
       </c>
       <c r="B39">
-        <v>-7.544820787571342</v>
+        <v>-8.1306381697204</v>
       </c>
       <c r="C39">
         <v>218.7117598010542</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.270650241396833</v>
+        <v>-8.7085303562956629</v>
       </c>
       <c r="B40">
-        <v>-8.1803500870885859</v>
+        <v>-8.7795965818140154</v>
       </c>
       <c r="C40">
         <v>218.7117598010542</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.3823903198229885</v>
+        <v>-8.7655560417534684</v>
       </c>
       <c r="B41">
-        <v>-8.8320031770408765</v>
+        <v>-9.4444986903301249</v>
       </c>
       <c r="C41">
         <v>218.7117598010542</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.3823903198229885</v>
+        <v>-8.7655560417534684</v>
       </c>
       <c r="B42">
-        <v>-8.8320031770408765</v>
+        <v>-9.4444986903301249</v>
       </c>
       <c r="C42">
         <v>218.7117598010542</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.1705086438757952</v>
+        <v>-8.5822493235921744</v>
       </c>
       <c r="B43">
-        <v>-8.2592614030734417</v>
+        <v>-8.8659724098879646</v>
       </c>
       <c r="C43">
         <v>218.7117598010542</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.9553637641570951</v>
+        <v>-8.3973207688914471</v>
       </c>
       <c r="B44">
-        <v>-7.6890910251123614</v>
+        <v>-8.2885554605234386</v>
       </c>
       <c r="C44">
         <v>218.7117598010542</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.7351265441588968</v>
+        <v>-8.20840282875688</v>
       </c>
       <c r="B45">
-        <v>-7.1229333979246432</v>
+        <v>-7.7138672382129814</v>
       </c>
       <c r="C45">
         <v>218.7117598010542</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.5079678473732034</v>
+        <v>-8.013127954294065</v>
       </c>
       <c r="B46">
-        <v>-6.56222987627728</v>
+        <v>-7.14352713893303</v>
       </c>
       <c r="C46">
         <v>218.7117598010542</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.2723305459888525</v>
+        <v>-7.809474687420245</v>
       </c>
       <c r="B47">
-        <v>-6.0082074727981691</v>
+        <v>-6.5789178336364378</v>
       </c>
       <c r="C47">
         <v>218.7117598010542</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.0277455469819863</v>
+        <v>-7.59680593329923</v>
       </c>
       <c r="B48">
-        <v>-5.4612358315587874</v>
+        <v>-6.0204750931817346</v>
       </c>
       <c r="C48">
         <v>218.7117598010542</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.7740157660255793</v>
+        <v>-7.3748306879064671</v>
       </c>
       <c r="B49">
-        <v>-4.9214702544914983</v>
+        <v>-5.4683979634038709</v>
       </c>
       <c r="C49">
         <v>218.7117598010542</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.5109441187926</v>
+        <v>-7.1432579472174167</v>
       </c>
       <c r="B50">
-        <v>-4.389066043528679</v>
+        <v>-4.9228854901378005</v>
       </c>
       <c r="C50">
         <v>218.7117598010542</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.2384380133110122</v>
+        <v>-6.9019310723394174</v>
       </c>
       <c r="B51">
-        <v>-3.86409616090125</v>
+        <v>-4.3840448138920545</v>
       </c>
       <c r="C51">
         <v>218.7117598010542</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.9568228270287245</v>
+        <v>-6.6512308849073634</v>
       </c>
       <c r="B52">
-        <v>-3.3463042100343419</v>
+        <v>-3.8516154538694942</v>
       </c>
       <c r="C52">
         <v>218.7117598010542</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.6665284297486425</v>
+        <v>-6.39167257168804</v>
       </c>
       <c r="B53">
-        <v>-2.8353514546516352</v>
+        <v>-3.3252450239465605</v>
       </c>
       <c r="C53">
         <v>218.7117598010542</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.3679846912736613</v>
+        <v>-6.1237713194482257</v>
       </c>
       <c r="B54">
-        <v>-2.3308991584768064</v>
+        <v>-2.8045811379996883</v>
       </c>
       <c r="C54">
         <v>218.7117598010542</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.0615397554822721</v>
+        <v>-5.8479412132422528</v>
       </c>
       <c r="B55">
-        <v>-1.83267298504745</v>
+        <v>-2.2893405631577579</v>
       </c>
       <c r="C55">
         <v>218.7117598010542</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.7472148625553263</v>
+        <v>-5.5641919312746451</v>
       </c>
       <c r="B56">
-        <v>-1.3406561971568096</v>
+        <v>-1.7795166795594002</v>
       </c>
       <c r="C56">
         <v>218.7117598010542</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.4249495267492644</v>
+        <v>-5.2724320500374784</v>
       </c>
       <c r="B57">
-        <v>-0.85489645741204134</v>
+        <v>-1.275172020595682</v>
       </c>
       <c r="C57">
         <v>218.7117598010542</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.0946832623205269</v>
+        <v>-4.9725701460228269</v>
       </c>
       <c r="B58">
-        <v>-0.37544142842030381</v>
+        <v>-0.77636911965767685</v>
       </c>
       <c r="C58">
         <v>218.7117598010542</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7563634369383045</v>
+        <v>-4.6645263993651911</v>
       </c>
       <c r="B59">
-        <v>0.097667415679886849</v>
+        <v>-0.28316257328162181</v>
       </c>
       <c r="C59">
         <v>218.7117598010542</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.4099688319228072</v>
+        <v>-4.3482674047687979</v>
       </c>
       <c r="B60">
-        <v>0.56441335462454945</v>
+        <v>0.20442476941553142</v>
       </c>
       <c r="C60">
         <v>218.7117598010542</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.0554860820069933</v>
+        <v>-4.0237713605803043</v>
       </c>
       <c r="B61">
-        <v>1.024785856618339</v>
+        <v>0.6863779961716594</v>
       </c>
       <c r="C61">
         <v>218.7117598010542</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.6929018219238277</v>
+        <v>-3.6910164651463648</v>
       </c>
       <c r="B62">
-        <v>1.4787743898659111</v>
+        <v>1.1626821947246366</v>
       </c>
       <c r="C62">
         <v>218.7117598010542</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.3222917273663271</v>
+        <v>-3.3500948846919125</v>
       </c>
       <c r="B63">
-        <v>1.926438586614722</v>
+        <v>1.6334004064816203</v>
       </c>
       <c r="C63">
         <v>218.7117598010542</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.9440876378677334</v>
+        <v>-3.0015546569549856</v>
       </c>
       <c r="B64">
-        <v>2.3681187352834345</v>
+        <v>2.0989074875269</v>
       </c>
       <c r="C64">
         <v>218.7117598010542</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.5588104339213507</v>
+        <v>-2.6460577875519014</v>
       </c>
       <c r="B65">
-        <v>2.8042252883335079</v>
+        <v>2.5596562476140416</v>
       </c>
       <c r="C65">
         <v>218.7117598010542</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.1669809960204773</v>
+        <v>-2.2842662820989754</v>
       </c>
       <c r="B66">
-        <v>3.2351686982264072</v>
+        <v>3.0160994964966177</v>
       </c>
       <c r="C66">
         <v>218.7117598010542</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.7684090374710912</v>
+        <v>-1.9159467464885212</v>
       </c>
       <c r="B67">
-        <v>3.6607990195467237</v>
+        <v>3.4680775933411025</v>
       </c>
       <c r="C67">
         <v>218.7117598010542</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.3600596028298719</v>
+        <v>-1.5372841877168495</v>
       </c>
       <c r="B68">
-        <v>4.0787247153715738</v>
+        <v>3.9129810949656059</v>
       </c>
       <c r="C68">
         <v>218.7117598010542</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.939559172607831</v>
+        <v>-1.1452997867292658</v>
       </c>
       <c r="B69">
-        <v>4.4870754585738934</v>
+        <v>4.3487724985320311</v>
       </c>
       <c r="C69">
         <v>218.7117598010542</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.510024639882626</v>
+        <v>-0.74394101916308231</v>
       </c>
       <c r="B70">
-        <v>4.8883073527173364</v>
+        <v>4.7781518649258041</v>
       </c>
       <c r="C70">
         <v>218.7117598010542</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.074853339901303009</v>
+        <v>-0.33751073969379369</v>
       </c>
       <c r="B71">
-        <v>5.2850974890589137</v>
+        <v>5.2040623331735993</v>
       </c>
       <c r="C71">
         <v>218.7117598010542</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.36692603597816409</v>
+        <v>0.07519297554237428</v>
       </c>
       <c r="B72">
-        <v>5.6766804789382954</v>
+        <v>5.6256817911435073</v>
       </c>
       <c r="C72">
         <v>218.7117598010542</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.81687355336423</v>
+        <v>0.49611235078605381</v>
       </c>
       <c r="B73">
-        <v>6.0618269947510326</v>
+        <v>6.041681763580784</v>
       </c>
       <c r="C73">
         <v>218.7117598010542</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.2745356618419881</v>
+        <v>0.92464603324604644</v>
       </c>
       <c r="B74">
-        <v>6.44089443303355</v>
+        <v>6.4524735738979189</v>
       </c>
       <c r="C74">
         <v>218.7117598010542</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.7389501531340605</v>
+        <v>1.3595489117710826</v>
       </c>
       <c r="B75">
-        <v>6.8146410113827223</v>
+        <v>6.8589088741952553</v>
       </c>
       <c r="C75">
         <v>218.7117598010542</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.209133803536532</v>
+        <v>1.7995444188014584</v>
       </c>
       <c r="B76">
-        <v>7.1838415074963669</v>
+        <v>7.2618608326572858</v>
       </c>
       <c r="C76">
         <v>218.7117598010542</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.6842021789611348</v>
+        <v>2.243477809707088</v>
       </c>
       <c r="B77">
-        <v>7.54919285311449</v>
+        <v>7.6621192909688807</v>
       </c>
       <c r="C77">
         <v>218.7117598010542</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.1636870192086972</v>
+        <v>2.6907130879848045</v>
       </c>
       <c r="B78">
-        <v>7.9110640360448983</v>
+        <v>8.0601192687322438</v>
       </c>
       <c r="C78">
         <v>218.7117598010542</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.6466523920113176</v>
+        <v>3.1400216012382396</v>
       </c>
       <c r="B79">
-        <v>8.2701925684579756</v>
+        <v>8.4567011603112832</v>
       </c>
       <c r="C79">
         <v>218.7117598010542</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.1313135729622728</v>
+        <v>3.5890980534196433</v>
       </c>
       <c r="B80">
-        <v>8.627984808501493</v>
+        <v>8.85344178093166</v>
       </c>
       <c r="C80">
         <v>218.7117598010542</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.6129367633807368</v>
+        <v>4.0319129046244653</v>
       </c>
       <c r="B81">
-        <v>8.9881709771101885</v>
+        <v>9.2544653168706912</v>
       </c>
       <c r="C81">
         <v>218.7117598010542</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.0014818178659715</v>
+        <v>4.3548569528491843</v>
       </c>
       <c r="B82">
-        <v>9.42170247251343</v>
+        <v>9.7374801039709862</v>
       </c>
       <c r="C82">
         <v>218.7117598010542</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.1337482743464538</v>
+        <v>4.4267630830154676</v>
       </c>
       <c r="B1">
-        <v>10.378109979026366</v>
+        <v>10.698799310575614</v>
       </c>
       <c r="C1">
         <v>240.80649437282904</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.277235387683926</v>
+        <v>3.5036926596339875</v>
       </c>
       <c r="B2">
-        <v>10.227845823707289</v>
+        <v>10.541914290640451</v>
       </c>
       <c r="C2">
         <v>240.80649437282904</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.596988776967418</v>
+        <v>2.8140769641161318</v>
       </c>
       <c r="B3">
-        <v>9.946931506253641</v>
+        <v>10.235131784937954</v>
       </c>
       <c r="C3">
         <v>240.80649437282904</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2.9521990958337496</v>
+        <v>2.1683933057619238</v>
       </c>
       <c r="B4">
-        <v>9.6397361910655714</v>
+        <v>9.9001412323231843</v>
       </c>
       <c r="C4">
         <v>240.80649437282904</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.334750598360503</v>
+        <v>1.555805747093377</v>
       </c>
       <c r="B5">
-        <v>9.3122753426153224</v>
+        <v>9.5439002121039085</v>
       </c>
       <c r="C5">
         <v>240.80649437282904</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>1.7411798192046275</v>
+        <v>0.97173516469749011</v>
       </c>
       <c r="B6">
-        <v>8.96711611282227</v>
+        <v>9.1693489049862862</v>
       </c>
       <c r="C6">
         <v>240.80649437282904</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.1694219655459326</v>
+        <v>0.413476251696074</v>
       </c>
       <c r="B7">
-        <v>8.605788944848527</v>
+        <v>8.7782243445398667</v>
       </c>
       <c r="C7">
         <v>240.80649437282904</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.618175874988539</v>
+        <v>-0.12065244119483562</v>
       </c>
       <c r="B8">
-        <v>8.2292582720610117</v>
+        <v>8.3716061620165778</v>
       </c>
       <c r="C8">
         <v>240.80649437282904</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.085569618101325517</v>
+        <v>-0.63311040359842252</v>
       </c>
       <c r="B9">
-        <v>7.83891158552895</v>
+        <v>7.95107355572249</v>
       </c>
       <c r="C9">
         <v>240.80649437282904</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.43038766391511596</v>
+        <v>-1.1265215594559226</v>
       </c>
       <c r="B10">
-        <v>7.4362245278478056</v>
+        <v>7.5183113045662822</v>
       </c>
       <c r="C10">
         <v>240.80649437282904</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.93159178029809331</v>
+        <v>-1.6033895296415885</v>
       </c>
       <c r="B11">
-        <v>7.0226022900156906</v>
+        <v>7.0749269428129447</v>
       </c>
       <c r="C11">
         <v>240.80649437282904</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.4191184802238286</v>
+        <v>-2.065117191616189</v>
       </c>
       <c r="B12">
-        <v>6.598842227077041</v>
+        <v>6.621821235275136</v>
       </c>
       <c r="C12">
         <v>240.80649437282904</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.8908583221863011</v>
+        <v>-2.5088247522535694</v>
       </c>
       <c r="B13">
-        <v>6.1633808018589322</v>
+        <v>6.1571451135999062</v>
       </c>
       <c r="C13">
         <v>240.80649437282904</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.3455902170440197</v>
+        <v>-2.9328320734920812</v>
       </c>
       <c r="B14">
-        <v>5.71531293201671</v>
+        <v>5.6798197884498585</v>
       </c>
       <c r="C14">
         <v>240.80649437282904</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.7888316757958562</v>
+        <v>-3.3445403081150036</v>
       </c>
       <c r="B15">
-        <v>5.2587282467361787</v>
+        <v>5.1945974197154623</v>
       </c>
       <c r="C15">
         <v>240.80649437282904</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.225642386537289</v>
+        <v>-3.75073676668163</v>
       </c>
       <c r="B16">
-        <v>4.7973770327155529</v>
+        <v>4.7058360291736587</v>
       </c>
       <c r="C16">
         <v>240.80649437282904</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.652512145609851</v>
+        <v>-4.1466721000103526</v>
       </c>
       <c r="B17">
-        <v>4.32865749517224</v>
+        <v>4.210486136919422</v>
       </c>
       <c r="C17">
         <v>240.80649437282904</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.064876194588126</v>
+        <v>-4.526180058534897</v>
       </c>
       <c r="B18">
-        <v>3.8491861937675504</v>
+        <v>3.7045884943435765</v>
       </c>
       <c r="C18">
         <v>240.80649437282904</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.4625214477328221</v>
+        <v>-4.888963450891211</v>
       </c>
       <c r="B19">
-        <v>3.3588051874192368</v>
+        <v>3.1879522797023543</v>
       </c>
       <c r="C19">
         <v>240.80649437282904</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.84632273747618</v>
+        <v>-5.2361923502658065</v>
       </c>
       <c r="B20">
-        <v>2.858162909859157</v>
+        <v>2.6613287779683308</v>
       </c>
       <c r="C20">
         <v>240.80649437282904</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-5.2171548962504382</v>
+        <v>-5.5690368298451896</v>
       </c>
       <c r="B21">
-        <v>2.3479077948191724</v>
+        <v>2.1254692741140873</v>
       </c>
       <c r="C21">
         <v>240.80649437282904</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.5757330916933325</v>
+        <v>-5.88845457233322</v>
       </c>
       <c r="B22">
-        <v>1.8285699310375947</v>
+        <v>1.5809886806358682</v>
       </c>
       <c r="C22">
         <v>240.80649437282904</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.9221338322645627</v>
+        <v>-6.1945536985031637</v>
       </c>
       <c r="B23">
-        <v>1.3002060272785427</v>
+        <v>1.0279564201245992</v>
       </c>
       <c r="C23">
         <v>240.80649437282904</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.2562739616293195</v>
+        <v>-6.487229938645636</v>
       </c>
       <c r="B24">
-        <v>0.76275444731258635</v>
+        <v>0.46630554269487362</v>
       </c>
       <c r="C24">
         <v>240.80649437282904</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.5780703234527991</v>
+        <v>-6.7663790230512522</v>
       </c>
       <c r="B25">
-        <v>0.21615355491029367</v>
+        <v>-0.10403090153871973</v>
       </c>
       <c r="C25">
         <v>240.80649437282904</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.8874061202140835</v>
+        <v>-7.0318540281804776</v>
       </c>
       <c r="B26">
-        <v>-0.3396832213099672</v>
+        <v>-0.68314724979255015</v>
       </c>
       <c r="C26">
         <v>240.80649437282904</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.184029989647839</v>
+        <v>-7.2833374151731682</v>
       </c>
       <c r="B27">
-        <v>-0.90494219333865555</v>
+        <v>-1.2712473886068785</v>
       </c>
       <c r="C27">
         <v>240.80649437282904</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.4676569283026124</v>
+        <v>-7.520468991339027</v>
       </c>
       <c r="B28">
-        <v>-1.4798346083184226</v>
+        <v>-1.8685625918529112</v>
       </c>
       <c r="C28">
         <v>240.80649437282904</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.738001932726954</v>
+        <v>-7.7428885639877576</v>
       </c>
       <c r="B29">
-        <v>-2.0645717133919312</v>
+        <v>-2.4753241334018727</v>
       </c>
       <c r="C29">
         <v>240.80649437282904</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.9948823963241331</v>
+        <v>-7.9503768828990422</v>
       </c>
       <c r="B30">
-        <v>-2.6592888582245808</v>
+        <v>-3.0916727902561418</v>
       </c>
       <c r="C30">
         <v>240.80649437282904</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.2385252999162581</v>
+        <v>-8.1432784677324737</v>
       </c>
       <c r="B31">
-        <v>-3.2638178025727287</v>
+        <v>-3.7173873519427332</v>
       </c>
       <c r="C31">
         <v>240.80649437282904</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.4692600211801565</v>
+        <v>-8.32207878061762</v>
       </c>
       <c r="B32">
-        <v>-3.8779144087154775</v>
+        <v>-4.3521561111198279</v>
       </c>
       <c r="C32">
         <v>240.80649437282904</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.68741593779265</v>
+        <v>-8.4872632836840527</v>
       </c>
       <c r="B33">
-        <v>-4.501334538931931</v>
+        <v>-4.9956673604456068</v>
       </c>
       <c r="C33">
         <v>240.80649437282904</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.89312728887934</v>
+        <v>-8.6390586839649028</v>
       </c>
       <c r="B34">
-        <v>-5.1339786939649033</v>
+        <v>-5.647775535019405</v>
       </c>
       <c r="C34">
         <v>240.80649437282904</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-9.0857477593609115</v>
+        <v>-8.7766566681075311</v>
       </c>
       <c r="B35">
-        <v>-5.7763259284120334</v>
+        <v>-6.3089996397051609</v>
       </c>
       <c r="C35">
         <v>240.80649437282904</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-9.2644358956068285</v>
+        <v>-8.89899016766286</v>
       </c>
       <c r="B36">
-        <v>-6.42899993533468</v>
+        <v>-6.9800248218079792</v>
       </c>
       <c r="C36">
         <v>240.80649437282904</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.4283502439865519</v>
+        <v>-9.004992114181821</v>
       </c>
       <c r="B37">
-        <v>-7.0926244077942018</v>
+        <v>-7.6615362286329534</v>
       </c>
       <c r="C37">
         <v>240.80649437282904</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.5761877509571622</v>
+        <v>-9.0929785835822816</v>
       </c>
       <c r="B38">
-        <v>-7.7681651808928542</v>
+        <v>-8.3546150804596859</v>
       </c>
       <c r="C38">
         <v>240.80649437282904</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.7047989633262119</v>
+        <v>-9.1587982292499266</v>
       </c>
       <c r="B39">
-        <v>-8.45795665789649</v>
+        <v>-9.0619268894657488</v>
       </c>
       <c r="C39">
         <v>240.80649437282904</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.8105728279888673</v>
+        <v>-9.1976828489374</v>
       </c>
       <c r="B40">
-        <v>-9.1646753841118649</v>
+        <v>-9.7865332408032248</v>
       </c>
       <c r="C40">
         <v>240.80649437282904</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.8898982918403</v>
+        <v>-9.2048642403973453</v>
       </c>
       <c r="B41">
-        <v>-9.890997904845733</v>
+        <v>-10.531495719624189</v>
       </c>
       <c r="C41">
         <v>240.80649437282904</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.8898982918403</v>
+        <v>-9.2048642403973453</v>
       </c>
       <c r="B42">
-        <v>-9.890997904845733</v>
+        <v>-10.531495719624189</v>
       </c>
       <c r="C42">
         <v>240.80649437282904</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.6548952228000537</v>
+        <v>-8.9880342295408031</v>
       </c>
       <c r="B43">
-        <v>-9.2800650367806963</v>
+        <v>-9.9211452113112735</v>
       </c>
       <c r="C43">
         <v>240.80649437282904</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.42018015042088</v>
+        <v>-8.7755064827746985</v>
       </c>
       <c r="B44">
-        <v>-8.6689187029788837</v>
+        <v>-9.3080322891626448</v>
       </c>
       <c r="C44">
         <v>240.80649437282904</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-9.18277522357188</v>
+        <v>-8.56317602707702</v>
       </c>
       <c r="B45">
-        <v>-8.0597661137020218</v>
+        <v>-8.6947926896261034</v>
       </c>
       <c r="C45">
         <v>240.80649437282904</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.9397025911221633</v>
+        <v>-8.3469378894257478</v>
       </c>
       <c r="B46">
-        <v>-7.4548144792118318</v>
+        <v>-8.0840621491494584</v>
       </c>
       <c r="C46">
         <v>240.80649437282904</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.6884140980428288</v>
+        <v>-8.1232705357018489</v>
       </c>
       <c r="B47">
-        <v>-6.85595251512271</v>
+        <v>-7.478101787545179</v>
       </c>
       <c r="C47">
         <v>240.80649437282904</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.4280803737129819</v>
+        <v>-7.8909861873981759</v>
       </c>
       <c r="B48">
-        <v>-6.2637949584596946</v>
+        <v>-6.8776742580844141</v>
       </c>
       <c r="C48">
         <v>240.80649437282904</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-8.1583017436137233</v>
+        <v>-7.649480504910553</v>
       </c>
       <c r="B49">
-        <v>-5.6786380516004851</v>
+        <v>-6.2831675974029775</v>
       </c>
       <c r="C49">
         <v>240.80649437282904</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.8786785332261529</v>
+        <v>-7.3981491486348023</v>
       </c>
       <c r="B50">
-        <v>-5.1007780369227831</v>
+        <v>-5.6949698421366843</v>
       </c>
       <c r="C50">
         <v>240.80649437282904</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.5889792405714767</v>
+        <v>-7.1366182892891645</v>
       </c>
       <c r="B51">
-        <v>-4.5303865057925661</v>
+        <v>-5.1133210219904637</v>
       </c>
       <c r="C51">
         <v>240.80649437282904</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.2896450538313067</v>
+        <v>-6.865436138881515</v>
       </c>
       <c r="B52">
-        <v>-3.9671364455288738</v>
+        <v>-4.5378691389456831</v>
       </c>
       <c r="C52">
         <v>240.80649437282904</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.9812853337273495</v>
+        <v>-6.5853814197421405</v>
       </c>
       <c r="B53">
-        <v>-3.41057619243902</v>
+        <v>-3.9681141880528181</v>
       </c>
       <c r="C53">
         <v>240.80649437282904</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.66450944098132</v>
+        <v>-6.2972328542013321</v>
       </c>
       <c r="B54">
-        <v>-2.860254082830314</v>
+        <v>-3.4035561643623442</v>
       </c>
       <c r="C54">
         <v>240.80649437282904</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.3398039813830538</v>
+        <v>-6.0016068986360507</v>
       </c>
       <c r="B55">
-        <v>-2.3158094400787368</v>
+        <v>-2.8437992512556134</v>
       </c>
       <c r="C55">
         <v>240.80649437282904</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.0071645409948724</v>
+        <v>-5.6984709456099507</v>
       </c>
       <c r="B56">
-        <v>-1.7772455358349184</v>
+        <v>-2.2888643854374413</v>
       </c>
       <c r="C56">
         <v>240.80649437282904</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.6664639509472234</v>
+        <v>-5.3876301217333555</v>
       </c>
       <c r="B57">
-        <v>-1.244656628818148</v>
+        <v>-1.7388766919435104</v>
       </c>
       <c r="C57">
         <v>240.80649437282904</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.317575042370561</v>
+        <v>-5.0688895536165974</v>
       </c>
       <c r="B58">
-        <v>-0.71813697774772811</v>
+        <v>-1.1939612958095143</v>
       </c>
       <c r="C58">
         <v>240.80649437282904</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.9603865758557912</v>
+        <v>-4.7420784700617151</v>
       </c>
       <c r="B59">
-        <v>-0.19776903428239939</v>
+        <v>-0.65422784644562915</v>
       </c>
       <c r="C59">
         <v>240.80649437282904</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.5948510298356986</v>
+        <v>-4.4071225086376318</v>
       </c>
       <c r="B60">
-        <v>0.31641197816128153</v>
+        <v>-0.11972409076003737</v>
       </c>
       <c r="C60">
         <v>240.80649437282904</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.2209368122035285</v>
+        <v>-4.0639714091049806</v>
       </c>
       <c r="B61">
-        <v>0.82438264322730981</v>
+        <v>0.40951769996459048</v>
       </c>
       <c r="C61">
         <v>240.80649437282904</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.8386123308525284</v>
+        <v>-3.7125749112243986</v>
       </c>
       <c r="B62">
-        <v>1.3261195445596792</v>
+        <v>0.93346525444557793</v>
       </c>
       <c r="C62">
         <v>240.80649437282904</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.4479880978574111</v>
+        <v>-3.3530767518792879</v>
       </c>
       <c r="B63">
-        <v>1.8217045947102986</v>
+        <v>1.452210863799196</v>
       </c>
       <c r="C63">
         <v>240.80649437282904</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-3.0497430420187346</v>
+        <v>-2.9863966564441005</v>
       </c>
       <c r="B64">
-        <v>2.3116410218627546</v>
+        <v>1.9663450687375104</v>
       </c>
       <c r="C64">
         <v>240.80649437282904</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.644698196318525</v>
+        <v>-2.6136483474160559</v>
       </c>
       <c r="B65">
-        <v>2.7965373831085425</v>
+        <v>2.4765829723715305</v>
       </c>
       <c r="C65">
         <v>240.80649437282904</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2336745937388041</v>
+        <v>-2.2359455472923706</v>
       </c>
       <c r="B66">
-        <v>3.2770022355391673</v>
+        <v>2.9836396778122687</v>
       </c>
       <c r="C66">
         <v>240.80649437282904</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.8163907666015771</v>
+        <v>-1.8529194400108713</v>
       </c>
       <c r="B67">
-        <v>3.7528269527593121</v>
+        <v>3.4872783742616016</v>
       </c>
       <c r="C67">
         <v>240.80649437282904</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-1.3881552445887591</v>
+        <v>-1.4582710552718108</v>
       </c>
       <c r="B68">
-        <v>4.22053417442641</v>
+        <v>3.9834545952848814</v>
       </c>
       <c r="C68">
         <v>240.80649437282904</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.94530937754082567</v>
+        <v>-1.0470955578686543</v>
       </c>
       <c r="B69">
-        <v>4.6774120758651456</v>
+        <v>4.4690190259280183</v>
       </c>
       <c r="C69">
         <v>240.80649437282904</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.49273579857257155</v>
+        <v>-0.62599480720527045</v>
       </c>
       <c r="B70">
-        <v>5.1270797090165026</v>
+        <v>4.9482106127957186</v>
       </c>
       <c r="C70">
         <v>240.80649437282904</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-0.035756914119593461</v>
+        <v>-0.20216559939252327</v>
       </c>
       <c r="B71">
-        <v>5.5734820897947515</v>
+        <v>5.4256503016810722</v>
       </c>
       <c r="C71">
         <v>240.80649437282904</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.42708705937362107</v>
+        <v>0.22632221724115142</v>
       </c>
       <c r="B72">
-        <v>6.01553721339106</v>
+        <v>5.9000987735719344</v>
       </c>
       <c r="C72">
         <v>240.80649437282904</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>0.89816647703661912</v>
+        <v>0.66262172230479621</v>
       </c>
       <c r="B73">
-        <v>6.4514881510887436</v>
+        <v>6.3695314873071744</v>
       </c>
       <c r="C73">
         <v>240.80649437282904</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.3767117903039785</v>
+        <v>1.1056507593749421</v>
       </c>
       <c r="B74">
-        <v>6.8819052992628551</v>
+        <v>6.8346432779349806</v>
       </c>
       <c r="C74">
         <v>240.80649437282904</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.8611575750624734</v>
+        <v>1.5532517599886275</v>
       </c>
       <c r="B75">
-        <v>7.3079489644615636</v>
+        <v>7.2968194850924171</v>
       </c>
       <c r="C75">
         <v>240.80649437282904</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.3498948087026439</v>
+        <v>2.0032007435574353</v>
       </c>
       <c r="B76">
-        <v>7.73081176883381</v>
+        <v>7.7574880905627142</v>
       </c>
       <c r="C76">
         <v>240.80649437282904</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.8414619613329264</v>
+        <v>2.453468081671367</v>
       </c>
       <c r="B77">
-        <v>8.1515770115885484</v>
+        <v>8.2179522857546985</v>
       </c>
       <c r="C77">
         <v>240.80649437282904</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.3350310724295911</v>
+        <v>2.9028679667595543</v>
       </c>
       <c r="B78">
-        <v>8.5708583845740058</v>
+        <v>8.6789734584333651</v>
       </c>
       <c r="C78">
         <v>240.80649437282904</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>3.8290407028900573</v>
+        <v>3.3492223153416369</v>
       </c>
       <c r="B79">
-        <v>8.9898132406123317</v>
+        <v>9.1419501205949647</v>
       </c>
       <c r="C79">
         <v>240.80649437282904</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.3205959284216524</v>
+        <v>3.7885475060023031</v>
       </c>
       <c r="B80">
-        <v>9.4105873238407742</v>
+        <v>9.6094400907933046</v>
       </c>
       <c r="C80">
         <v>240.80649437282904</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>4.8022052818762138</v>
+        <v>4.21066148413964</v>
       </c>
       <c r="B81">
-        <v>9.83873337764305</v>
+        <v>10.087981100770804</v>
       </c>
       <c r="C81">
         <v>240.80649437282904</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.1337482743464538</v>
+        <v>4.4267630830154676</v>
       </c>
       <c r="B82">
-        <v>10.378109979026366</v>
+        <v>10.698799310575614</v>
       </c>
       <c r="C82">
         <v>240.80649437282904</v>
